--- a/144/DQ Templates and Instructions/Topic 4 DQ 1/Topic 4 DQ 1.xlsx
+++ b/144/DQ Templates and Instructions/Topic 4 DQ 1/Topic 4 DQ 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail.sharepoint.com/sites/MathematicsProgramFacultyStaff-MATOFTF/Shared Documents/MATOFTF/ALEKS/DQ Templates and Instructions/Topic 4 DQ 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="403" documentId="8_{3C829CDA-585B-40ED-A74D-EC300311E87A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C646E81C-6553-498C-B4D9-F40FE6F06C7D}"/>
+  <xr:revisionPtr revIDLastSave="412" documentId="8_{3C829CDA-585B-40ED-A74D-EC300311E87A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01E5E134-2164-4823-8E2C-54CF50B12056}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="12852" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{205DC2E6-2D69-4C44-AD14-EEFE253664E7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{205DC2E6-2D69-4C44-AD14-EEFE253664E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Goals and Instructions" sheetId="3" r:id="rId1"/>
@@ -39,6 +39,51 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={A0985028-5FBA-4FA8-8E71-7E8CFEA90D54}</author>
+    <author>tc={429557F3-0EF1-498A-943D-63A2EC685223}</author>
+  </authors>
+  <commentList>
+    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{A0985028-5FBA-4FA8-8E71-7E8CFEA90D54}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    https://www.loom.com/share/164e175af2174039badfd71587558e62?sid=054699c1-4529-4616-90c4-d5b8f8b5cb60</t>
+      </text>
+    </comment>
+    <comment ref="D3" authorId="1" shapeId="0" xr:uid="{429557F3-0EF1-498A-943D-63A2EC685223}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    https://www.loom.com/share/a16ca2cd6aec4989bef278e4bf0ddc51?sid=6af98c1c-096f-4d69-a889-8daa7bbcde9d</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={E99B54CE-8E56-445E-8DD0-01CDEAF4F008}</author>
+  </authors>
+  <commentList>
+    <comment ref="G8" authorId="0" shapeId="0" xr:uid="{E99B54CE-8E56-445E-8DD0-01CDEAF4F008}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    https://www.loom.com/share/c125402a2f7e4288a18dc9f899e63e93</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -429,7 +474,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -521,6 +566,33 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="12">
@@ -1095,7 +1167,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
@@ -1278,6 +1350,9 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1444,6 +1519,24 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1459,39 +1552,30 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1501,17 +1585,19 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1788,7 +1874,9 @@
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Richard Ketchersid" id="{358B6DF9-6FBE-437F-8549-1F3EB522A659}" userId="S::richard.ketchersid@gcu.edu::a14ec2f7-27bd-40c3-90d9-209834cdef57" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2086,6 +2174,43 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="D2" dT="2026-07-16T19:40:49.11" personId="{358B6DF9-6FBE-437F-8549-1F3EB522A659}" id="{A0985028-5FBA-4FA8-8E71-7E8CFEA90D54}">
+    <text>https://www.loom.com/share/164e175af2174039badfd71587558e62?sid=054699c1-4529-4616-90c4-d5b8f8b5cb60</text>
+    <extLst>
+      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
+        <xltc2:checksum>2591543169</xltc2:checksum>
+        <xltc2:hyperlink startIndex="0" length="100" url="https://www.loom.com/share/164e175af2174039badfd71587558e62?sid=054699c1-4529-4616-90c4-d5b8f8b5cb60"/>
+      </x:ext>
+    </extLst>
+  </threadedComment>
+  <threadedComment ref="D3" dT="2026-07-16T19:41:05.75" personId="{358B6DF9-6FBE-437F-8549-1F3EB522A659}" id="{429557F3-0EF1-498A-943D-63A2EC685223}">
+    <text>https://www.loom.com/share/a16ca2cd6aec4989bef278e4bf0ddc51?sid=6af98c1c-096f-4d69-a889-8daa7bbcde9d</text>
+    <extLst>
+      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
+        <xltc2:checksum>4172717784</xltc2:checksum>
+        <xltc2:hyperlink startIndex="0" length="100" url="https://www.loom.com/share/a16ca2cd6aec4989bef278e4bf0ddc51?sid=6af98c1c-096f-4d69-a889-8daa7bbcde9d"/>
+      </x:ext>
+    </extLst>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="G8" dT="2026-07-16T19:42:01.98" personId="{358B6DF9-6FBE-437F-8549-1F3EB522A659}" id="{E99B54CE-8E56-445E-8DD0-01CDEAF4F008}">
+    <text>https://www.loom.com/share/c125402a2f7e4288a18dc9f899e63e93</text>
+    <extLst>
+      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
+        <xltc2:checksum>2558475489</xltc2:checksum>
+        <xltc2:hyperlink startIndex="0" length="59" url="https://www.loom.com/share/c125402a2f7e4288a18dc9f899e63e93"/>
+      </x:ext>
+    </extLst>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F05F4483-7C1E-488E-B02A-A78D2EB4BCC6}">
   <dimension ref="B2:I11"/>
@@ -2098,55 +2223,55 @@
       <c r="B2" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="62" t="s">
+      <c r="D2" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="65"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="65"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="67"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="68"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B4" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="65"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="67"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="68"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B5" s="56" t="s">
         <v>72</v>
       </c>
-      <c r="D5" s="65"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="67"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="68"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D6" s="68"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="70"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="71"/>
     </row>
     <row r="8" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B8" s="57" t="s">
@@ -2182,14 +2307,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DCC803D-65A0-4D9D-9D2F-35F6192494FC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DCC803D-65A0-4D9D-9D2F-35F6192494FC}">
   <dimension ref="B1:S40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" customWidth="1"/>
     <col min="2" max="2" width="37.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.5703125" customWidth="1"/>
-    <col min="4" max="4" width="22.85546875" customWidth="1"/>
+    <col min="4" max="4" width="23.7109375" customWidth="1"/>
     <col min="5" max="5" width="19.42578125" customWidth="1"/>
     <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="4.7109375" customWidth="1"/>
@@ -2199,54 +2324,54 @@
       <c r="D1" s="33"/>
     </row>
     <row r="2" spans="2:11" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="129" t="s">
+      <c r="B2" s="62" t="s">
         <v>74</v>
       </c>
       <c r="C2" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="34" t="s">
+      <c r="D2" s="133" t="s">
         <v>52</v>
       </c>
       <c r="E2" s="27"/>
     </row>
     <row r="3" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D3" s="83" t="s">
+      <c r="D3" s="134" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="100" t="s">
+      <c r="E3" s="101" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="101"/>
-      <c r="G3" s="101"/>
-      <c r="H3" s="101"/>
-      <c r="I3" s="102"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="103"/>
     </row>
     <row r="4" spans="2:11" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="84"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="104"/>
-      <c r="I4" s="105"/>
+      <c r="D4" s="135"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="105"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="105"/>
+      <c r="I4" s="106"/>
     </row>
     <row r="5" spans="2:11" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D5" s="33"/>
+      <c r="D5" s="136"/>
     </row>
     <row r="6" spans="2:11" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="81"/>
-      <c r="E6" s="106" t="s">
+      <c r="C6" s="82"/>
+      <c r="E6" s="107" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="107"/>
-      <c r="G6" s="107"/>
-      <c r="H6" s="107"/>
-      <c r="I6" s="107"/>
-      <c r="J6" s="107"/>
-      <c r="K6" s="108"/>
+      <c r="F6" s="108"/>
+      <c r="G6" s="108"/>
+      <c r="H6" s="108"/>
+      <c r="I6" s="108"/>
+      <c r="J6" s="108"/>
+      <c r="K6" s="109"/>
     </row>
     <row r="7" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
@@ -2258,14 +2383,14 @@
       <c r="E7" s="32">
         <v>15</v>
       </c>
-      <c r="F7" s="85" t="s">
+      <c r="F7" s="86" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="86"/>
-      <c r="H7" s="86"/>
-      <c r="I7" s="86"/>
-      <c r="J7" s="86"/>
-      <c r="K7" s="87"/>
+      <c r="G7" s="87"/>
+      <c r="H7" s="87"/>
+      <c r="I7" s="87"/>
+      <c r="J7" s="87"/>
+      <c r="K7" s="88"/>
     </row>
     <row r="8" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
@@ -2277,14 +2402,14 @@
       <c r="E8" s="29">
         <v>15</v>
       </c>
-      <c r="F8" s="88" t="s">
+      <c r="F8" s="89" t="s">
         <v>58</v>
       </c>
-      <c r="G8" s="89"/>
-      <c r="H8" s="89"/>
-      <c r="I8" s="89"/>
-      <c r="J8" s="89"/>
-      <c r="K8" s="90"/>
+      <c r="G8" s="90"/>
+      <c r="H8" s="90"/>
+      <c r="I8" s="90"/>
+      <c r="J8" s="90"/>
+      <c r="K8" s="91"/>
     </row>
     <row r="9" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
@@ -2296,14 +2421,14 @@
       <c r="E9" s="30">
         <v>16</v>
       </c>
-      <c r="F9" s="85" t="s">
+      <c r="F9" s="86" t="s">
         <v>59</v>
       </c>
-      <c r="G9" s="86"/>
-      <c r="H9" s="86"/>
-      <c r="I9" s="86"/>
-      <c r="J9" s="86"/>
-      <c r="K9" s="87"/>
+      <c r="G9" s="87"/>
+      <c r="H9" s="87"/>
+      <c r="I9" s="87"/>
+      <c r="J9" s="87"/>
+      <c r="K9" s="88"/>
     </row>
     <row r="10" spans="2:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="8" t="s">
@@ -2315,14 +2440,14 @@
       <c r="E10" s="31">
         <v>16</v>
       </c>
-      <c r="F10" s="97" t="s">
+      <c r="F10" s="98" t="s">
         <v>60</v>
       </c>
-      <c r="G10" s="98"/>
-      <c r="H10" s="98"/>
-      <c r="I10" s="98"/>
-      <c r="J10" s="98"/>
-      <c r="K10" s="99"/>
+      <c r="G10" s="99"/>
+      <c r="H10" s="99"/>
+      <c r="I10" s="99"/>
+      <c r="J10" s="99"/>
+      <c r="K10" s="100"/>
     </row>
     <row r="11" spans="2:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="9" t="s">
@@ -2333,38 +2458,38 @@
       </c>
     </row>
     <row r="12" spans="2:11" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F12" s="82" t="s">
+      <c r="F12" s="83" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="63"/>
-      <c r="H12" s="63"/>
-      <c r="I12" s="63"/>
-      <c r="J12" s="63"/>
-      <c r="K12" s="64"/>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="64"/>
+      <c r="K12" s="65"/>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B13" s="91" t="s">
+      <c r="B13" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="92"/>
-      <c r="D13" s="93"/>
-      <c r="F13" s="65"/>
-      <c r="G13" s="109"/>
-      <c r="H13" s="109"/>
-      <c r="I13" s="109"/>
-      <c r="J13" s="109"/>
-      <c r="K13" s="67"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="94"/>
+      <c r="F13" s="66"/>
+      <c r="G13" s="110"/>
+      <c r="H13" s="110"/>
+      <c r="I13" s="110"/>
+      <c r="J13" s="110"/>
+      <c r="K13" s="68"/>
     </row>
     <row r="14" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="94"/>
-      <c r="C14" s="95"/>
-      <c r="D14" s="96"/>
-      <c r="F14" s="68"/>
-      <c r="G14" s="69"/>
-      <c r="H14" s="69"/>
-      <c r="I14" s="69"/>
-      <c r="J14" s="69"/>
-      <c r="K14" s="70"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="96"/>
+      <c r="D14" s="97"/>
+      <c r="F14" s="69"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="70"/>
+      <c r="J14" s="70"/>
+      <c r="K14" s="71"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F15" s="35" t="s">
@@ -2503,10 +2628,10 @@
       <c r="K24" s="36"/>
     </row>
     <row r="25" spans="2:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="82" t="s">
+      <c r="B25" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="64"/>
+      <c r="C25" s="65"/>
       <c r="F25" s="36"/>
       <c r="G25" s="36"/>
       <c r="H25" s="36"/>
@@ -2515,8 +2640,8 @@
       <c r="K25" s="36"/>
     </row>
     <row r="26" spans="2:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="65"/>
-      <c r="C26" s="67"/>
+      <c r="B26" s="66"/>
+      <c r="C26" s="68"/>
       <c r="F26" s="36"/>
       <c r="G26" s="36"/>
       <c r="H26" s="36"/>
@@ -2525,8 +2650,8 @@
       <c r="K26" s="36"/>
     </row>
     <row r="27" spans="2:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="65"/>
-      <c r="C27" s="67"/>
+      <c r="B27" s="66"/>
+      <c r="C27" s="68"/>
       <c r="F27" s="36"/>
       <c r="G27" s="36"/>
       <c r="H27" s="36"/>
@@ -2535,217 +2660,217 @@
       <c r="K27" s="36"/>
     </row>
     <row r="28" spans="2:19" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="68"/>
-      <c r="C28" s="70"/>
+      <c r="B28" s="69"/>
+      <c r="C28" s="71"/>
     </row>
     <row r="29" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E29" s="71" t="s">
+      <c r="E29" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="F29" s="72"/>
-      <c r="G29" s="72"/>
-      <c r="H29" s="72"/>
-      <c r="I29" s="72"/>
-      <c r="J29" s="72"/>
-      <c r="K29" s="73"/>
-      <c r="M29" s="71" t="s">
+      <c r="F29" s="73"/>
+      <c r="G29" s="73"/>
+      <c r="H29" s="73"/>
+      <c r="I29" s="73"/>
+      <c r="J29" s="73"/>
+      <c r="K29" s="74"/>
+      <c r="M29" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="N29" s="72"/>
-      <c r="O29" s="72"/>
-      <c r="P29" s="72"/>
-      <c r="Q29" s="72"/>
-      <c r="R29" s="72"/>
-      <c r="S29" s="73"/>
+      <c r="N29" s="73"/>
+      <c r="O29" s="73"/>
+      <c r="P29" s="73"/>
+      <c r="Q29" s="73"/>
+      <c r="R29" s="73"/>
+      <c r="S29" s="74"/>
     </row>
     <row r="30" spans="2:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="82" t="s">
+      <c r="B30" s="83" t="s">
         <v>63</v>
       </c>
-      <c r="C30" s="64"/>
-      <c r="E30" s="74"/>
-      <c r="F30" s="75"/>
-      <c r="G30" s="75"/>
-      <c r="H30" s="75"/>
-      <c r="I30" s="75"/>
-      <c r="J30" s="75"/>
-      <c r="K30" s="76"/>
-      <c r="M30" s="74"/>
-      <c r="N30" s="75"/>
-      <c r="O30" s="75"/>
-      <c r="P30" s="75"/>
-      <c r="Q30" s="75"/>
-      <c r="R30" s="75"/>
-      <c r="S30" s="76"/>
+      <c r="C30" s="65"/>
+      <c r="E30" s="75"/>
+      <c r="F30" s="76"/>
+      <c r="G30" s="76"/>
+      <c r="H30" s="76"/>
+      <c r="I30" s="76"/>
+      <c r="J30" s="76"/>
+      <c r="K30" s="77"/>
+      <c r="M30" s="75"/>
+      <c r="N30" s="76"/>
+      <c r="O30" s="76"/>
+      <c r="P30" s="76"/>
+      <c r="Q30" s="76"/>
+      <c r="R30" s="76"/>
+      <c r="S30" s="77"/>
     </row>
     <row r="31" spans="2:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="65"/>
-      <c r="C31" s="67"/>
-      <c r="E31" s="74"/>
-      <c r="F31" s="75"/>
-      <c r="G31" s="75"/>
-      <c r="H31" s="75"/>
-      <c r="I31" s="75"/>
-      <c r="J31" s="75"/>
-      <c r="K31" s="76"/>
-      <c r="M31" s="74"/>
-      <c r="N31" s="75"/>
-      <c r="O31" s="75"/>
-      <c r="P31" s="75"/>
-      <c r="Q31" s="75"/>
-      <c r="R31" s="75"/>
-      <c r="S31" s="76"/>
+      <c r="B31" s="66"/>
+      <c r="C31" s="68"/>
+      <c r="E31" s="75"/>
+      <c r="F31" s="76"/>
+      <c r="G31" s="76"/>
+      <c r="H31" s="76"/>
+      <c r="I31" s="76"/>
+      <c r="J31" s="76"/>
+      <c r="K31" s="77"/>
+      <c r="M31" s="75"/>
+      <c r="N31" s="76"/>
+      <c r="O31" s="76"/>
+      <c r="P31" s="76"/>
+      <c r="Q31" s="76"/>
+      <c r="R31" s="76"/>
+      <c r="S31" s="77"/>
     </row>
     <row r="32" spans="2:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="65"/>
-      <c r="C32" s="67"/>
-      <c r="E32" s="74"/>
-      <c r="F32" s="75"/>
-      <c r="G32" s="75"/>
-      <c r="H32" s="75"/>
-      <c r="I32" s="75"/>
-      <c r="J32" s="75"/>
-      <c r="K32" s="76"/>
-      <c r="M32" s="74"/>
-      <c r="N32" s="75"/>
-      <c r="O32" s="75"/>
-      <c r="P32" s="75"/>
-      <c r="Q32" s="75"/>
-      <c r="R32" s="75"/>
-      <c r="S32" s="76"/>
+      <c r="B32" s="66"/>
+      <c r="C32" s="68"/>
+      <c r="E32" s="75"/>
+      <c r="F32" s="76"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="76"/>
+      <c r="I32" s="76"/>
+      <c r="J32" s="76"/>
+      <c r="K32" s="77"/>
+      <c r="M32" s="75"/>
+      <c r="N32" s="76"/>
+      <c r="O32" s="76"/>
+      <c r="P32" s="76"/>
+      <c r="Q32" s="76"/>
+      <c r="R32" s="76"/>
+      <c r="S32" s="77"/>
     </row>
     <row r="33" spans="2:19" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="68"/>
-      <c r="C33" s="70"/>
-      <c r="E33" s="74"/>
-      <c r="F33" s="75"/>
-      <c r="G33" s="75"/>
-      <c r="H33" s="75"/>
-      <c r="I33" s="75"/>
-      <c r="J33" s="75"/>
-      <c r="K33" s="76"/>
-      <c r="M33" s="74"/>
-      <c r="N33" s="75"/>
-      <c r="O33" s="75"/>
-      <c r="P33" s="75"/>
-      <c r="Q33" s="75"/>
-      <c r="R33" s="75"/>
-      <c r="S33" s="76"/>
+      <c r="B33" s="69"/>
+      <c r="C33" s="71"/>
+      <c r="E33" s="75"/>
+      <c r="F33" s="76"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="76"/>
+      <c r="I33" s="76"/>
+      <c r="J33" s="76"/>
+      <c r="K33" s="77"/>
+      <c r="M33" s="75"/>
+      <c r="N33" s="76"/>
+      <c r="O33" s="76"/>
+      <c r="P33" s="76"/>
+      <c r="Q33" s="76"/>
+      <c r="R33" s="76"/>
+      <c r="S33" s="77"/>
     </row>
     <row r="34" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="E34" s="74"/>
-      <c r="F34" s="75"/>
-      <c r="G34" s="75"/>
-      <c r="H34" s="75"/>
-      <c r="I34" s="75"/>
-      <c r="J34" s="75"/>
-      <c r="K34" s="76"/>
-      <c r="M34" s="74"/>
-      <c r="N34" s="75"/>
-      <c r="O34" s="75"/>
-      <c r="P34" s="75"/>
-      <c r="Q34" s="75"/>
-      <c r="R34" s="75"/>
-      <c r="S34" s="76"/>
+      <c r="E34" s="75"/>
+      <c r="F34" s="76"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="76"/>
+      <c r="I34" s="76"/>
+      <c r="J34" s="76"/>
+      <c r="K34" s="77"/>
+      <c r="M34" s="75"/>
+      <c r="N34" s="76"/>
+      <c r="O34" s="76"/>
+      <c r="P34" s="76"/>
+      <c r="Q34" s="76"/>
+      <c r="R34" s="76"/>
+      <c r="S34" s="77"/>
     </row>
     <row r="35" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="E35" s="74"/>
-      <c r="F35" s="75"/>
-      <c r="G35" s="75"/>
-      <c r="H35" s="75"/>
-      <c r="I35" s="75"/>
-      <c r="J35" s="75"/>
-      <c r="K35" s="76"/>
-      <c r="M35" s="74"/>
-      <c r="N35" s="75"/>
-      <c r="O35" s="75"/>
-      <c r="P35" s="75"/>
-      <c r="Q35" s="75"/>
-      <c r="R35" s="75"/>
-      <c r="S35" s="76"/>
+      <c r="E35" s="75"/>
+      <c r="F35" s="76"/>
+      <c r="G35" s="76"/>
+      <c r="H35" s="76"/>
+      <c r="I35" s="76"/>
+      <c r="J35" s="76"/>
+      <c r="K35" s="77"/>
+      <c r="M35" s="75"/>
+      <c r="N35" s="76"/>
+      <c r="O35" s="76"/>
+      <c r="P35" s="76"/>
+      <c r="Q35" s="76"/>
+      <c r="R35" s="76"/>
+      <c r="S35" s="77"/>
     </row>
     <row r="36" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="E36" s="74"/>
-      <c r="F36" s="75"/>
-      <c r="G36" s="75"/>
-      <c r="H36" s="75"/>
-      <c r="I36" s="75"/>
-      <c r="J36" s="75"/>
-      <c r="K36" s="76"/>
-      <c r="M36" s="74"/>
-      <c r="N36" s="75"/>
-      <c r="O36" s="75"/>
-      <c r="P36" s="75"/>
-      <c r="Q36" s="75"/>
-      <c r="R36" s="75"/>
-      <c r="S36" s="76"/>
+      <c r="E36" s="75"/>
+      <c r="F36" s="76"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="76"/>
+      <c r="I36" s="76"/>
+      <c r="J36" s="76"/>
+      <c r="K36" s="77"/>
+      <c r="M36" s="75"/>
+      <c r="N36" s="76"/>
+      <c r="O36" s="76"/>
+      <c r="P36" s="76"/>
+      <c r="Q36" s="76"/>
+      <c r="R36" s="76"/>
+      <c r="S36" s="77"/>
     </row>
     <row r="37" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="E37" s="74"/>
-      <c r="F37" s="75"/>
-      <c r="G37" s="75"/>
-      <c r="H37" s="75"/>
-      <c r="I37" s="75"/>
-      <c r="J37" s="75"/>
-      <c r="K37" s="76"/>
-      <c r="M37" s="74"/>
-      <c r="N37" s="75"/>
-      <c r="O37" s="75"/>
-      <c r="P37" s="75"/>
-      <c r="Q37" s="75"/>
-      <c r="R37" s="75"/>
-      <c r="S37" s="76"/>
+      <c r="E37" s="75"/>
+      <c r="F37" s="76"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="76"/>
+      <c r="I37" s="76"/>
+      <c r="J37" s="76"/>
+      <c r="K37" s="77"/>
+      <c r="M37" s="75"/>
+      <c r="N37" s="76"/>
+      <c r="O37" s="76"/>
+      <c r="P37" s="76"/>
+      <c r="Q37" s="76"/>
+      <c r="R37" s="76"/>
+      <c r="S37" s="77"/>
     </row>
     <row r="38" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="E38" s="74"/>
-      <c r="F38" s="75"/>
-      <c r="G38" s="75"/>
-      <c r="H38" s="75"/>
-      <c r="I38" s="75"/>
-      <c r="J38" s="75"/>
-      <c r="K38" s="76"/>
-      <c r="M38" s="74"/>
-      <c r="N38" s="75"/>
-      <c r="O38" s="75"/>
-      <c r="P38" s="75"/>
-      <c r="Q38" s="75"/>
-      <c r="R38" s="75"/>
-      <c r="S38" s="76"/>
+      <c r="E38" s="75"/>
+      <c r="F38" s="76"/>
+      <c r="G38" s="76"/>
+      <c r="H38" s="76"/>
+      <c r="I38" s="76"/>
+      <c r="J38" s="76"/>
+      <c r="K38" s="77"/>
+      <c r="M38" s="75"/>
+      <c r="N38" s="76"/>
+      <c r="O38" s="76"/>
+      <c r="P38" s="76"/>
+      <c r="Q38" s="76"/>
+      <c r="R38" s="76"/>
+      <c r="S38" s="77"/>
     </row>
     <row r="39" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="E39" s="74"/>
-      <c r="F39" s="75"/>
-      <c r="G39" s="75"/>
-      <c r="H39" s="75"/>
-      <c r="I39" s="75"/>
-      <c r="J39" s="75"/>
-      <c r="K39" s="76"/>
-      <c r="M39" s="74"/>
-      <c r="N39" s="75"/>
-      <c r="O39" s="75"/>
-      <c r="P39" s="75"/>
-      <c r="Q39" s="75"/>
-      <c r="R39" s="75"/>
-      <c r="S39" s="76"/>
+      <c r="E39" s="75"/>
+      <c r="F39" s="76"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="76"/>
+      <c r="I39" s="76"/>
+      <c r="J39" s="76"/>
+      <c r="K39" s="77"/>
+      <c r="M39" s="75"/>
+      <c r="N39" s="76"/>
+      <c r="O39" s="76"/>
+      <c r="P39" s="76"/>
+      <c r="Q39" s="76"/>
+      <c r="R39" s="76"/>
+      <c r="S39" s="77"/>
     </row>
     <row r="40" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E40" s="77"/>
-      <c r="F40" s="78"/>
-      <c r="G40" s="78"/>
-      <c r="H40" s="78"/>
-      <c r="I40" s="78"/>
-      <c r="J40" s="78"/>
-      <c r="K40" s="79"/>
-      <c r="M40" s="77"/>
-      <c r="N40" s="78"/>
-      <c r="O40" s="78"/>
-      <c r="P40" s="78"/>
-      <c r="Q40" s="78"/>
-      <c r="R40" s="78"/>
-      <c r="S40" s="79"/>
+      <c r="E40" s="78"/>
+      <c r="F40" s="79"/>
+      <c r="G40" s="79"/>
+      <c r="H40" s="79"/>
+      <c r="I40" s="79"/>
+      <c r="J40" s="79"/>
+      <c r="K40" s="80"/>
+      <c r="M40" s="78"/>
+      <c r="N40" s="79"/>
+      <c r="O40" s="79"/>
+      <c r="P40" s="79"/>
+      <c r="Q40" s="79"/>
+      <c r="R40" s="79"/>
+      <c r="S40" s="80"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="hjmGLKXeNlgl58dS+Rt35BYMo7L3MYYejTFyJr/fV+6XtxWmKgN1dTGnaPe/p1PI4pn+k+GPKJOzPS1EnQAlAw==" saltValue="HdGJLHn3jMVbU2JXT7Vd1w==" spinCount="100000" sheet="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="9l8gJOf7bmHg0E+pecKvgY9rbixgCaeEA9wQgFhyXrwKF3HW12rHp+16vcbnJSohe3eJoygMIRAvdBk1E9C+Qg==" saltValue="kCzTCaIjsc/v+OenjNhBNA==" spinCount="100000" sheet="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="14">
     <mergeCell ref="M29:S40"/>
     <mergeCell ref="B6:C6"/>
@@ -2774,6 +2899,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId3"/>
   <drawing r:id="rId4"/>
+  <legacyDrawing r:id="rId5"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -2797,7 +2923,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{049149D3-C31D-4474-A186-04CB99D57D70}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{049149D3-C31D-4474-A186-04CB99D57D70}">
   <dimension ref="B2:S22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2810,34 +2936,34 @@
     <row r="2" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:19" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="82" t="s">
+      <c r="B4" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="63" t="s">
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="64"/>
-      <c r="M4" s="80" t="s">
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="65"/>
+      <c r="M4" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="81"/>
+      <c r="N4" s="82"/>
     </row>
     <row r="5" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="65"/>
-      <c r="C5" s="109"/>
-      <c r="D5" s="109"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="109"/>
-      <c r="G5" s="109"/>
-      <c r="H5" s="109"/>
-      <c r="I5" s="109"/>
-      <c r="J5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="110"/>
+      <c r="G5" s="110"/>
+      <c r="H5" s="110"/>
+      <c r="I5" s="110"/>
+      <c r="J5" s="68"/>
       <c r="M5" s="3" t="s">
         <v>9</v>
       </c>
@@ -2846,15 +2972,15 @@
       </c>
     </row>
     <row r="6" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="65"/>
-      <c r="C6" s="109"/>
-      <c r="D6" s="109"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="70"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="110"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="71"/>
       <c r="M6" s="5" t="s">
         <v>11</v>
       </c>
@@ -2863,17 +2989,17 @@
       </c>
     </row>
     <row r="7" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="68"/>
-      <c r="C7" s="69"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="70"/>
+      <c r="B7" s="69"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="71"/>
       <c r="F7" s="58"/>
-      <c r="G7" s="120" t="s">
+      <c r="G7" s="111" t="s">
         <v>67</v>
       </c>
-      <c r="H7" s="121"/>
-      <c r="I7" s="121"/>
-      <c r="J7" s="122"/>
+      <c r="H7" s="112"/>
+      <c r="I7" s="112"/>
+      <c r="J7" s="113"/>
       <c r="M7" s="7" t="s">
         <v>13</v>
       </c>
@@ -2882,18 +3008,18 @@
       </c>
     </row>
     <row r="8" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="110" t="s">
+      <c r="B8" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="111"/>
-      <c r="D8" s="111"/>
-      <c r="E8" s="112"/>
+      <c r="C8" s="118"/>
+      <c r="D8" s="118"/>
+      <c r="E8" s="119"/>
       <c r="F8" s="50"/>
-      <c r="G8" s="130" t="s">
+      <c r="G8" s="114" t="s">
         <v>75</v>
       </c>
-      <c r="H8" s="131"/>
-      <c r="I8" s="132"/>
+      <c r="H8" s="115"/>
+      <c r="I8" s="116"/>
       <c r="J8" s="53"/>
       <c r="M8" s="8" t="s">
         <v>15</v>
@@ -2903,17 +3029,17 @@
       </c>
     </row>
     <row r="9" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="113"/>
-      <c r="C9" s="114"/>
-      <c r="D9" s="114"/>
-      <c r="E9" s="115"/>
+      <c r="B9" s="120"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="129"/>
       <c r="F9" s="59"/>
-      <c r="G9" s="120" t="s">
+      <c r="G9" s="111" t="s">
         <v>66</v>
       </c>
-      <c r="H9" s="121"/>
-      <c r="I9" s="121"/>
-      <c r="J9" s="122"/>
+      <c r="H9" s="112"/>
+      <c r="I9" s="112"/>
+      <c r="J9" s="113"/>
       <c r="M9" s="9" t="s">
         <v>17</v>
       </c>
@@ -2922,10 +3048,10 @@
       </c>
     </row>
     <row r="10" spans="2:19" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="116"/>
-      <c r="C10" s="117"/>
-      <c r="D10" s="117"/>
-      <c r="E10" s="118"/>
+      <c r="B10" s="123"/>
+      <c r="C10" s="124"/>
+      <c r="D10" s="124"/>
+      <c r="E10" s="125"/>
       <c r="F10" s="50"/>
       <c r="G10" s="51"/>
       <c r="H10" s="51"/>
@@ -2933,12 +3059,12 @@
       <c r="J10" s="53"/>
     </row>
     <row r="11" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="110" t="s">
+      <c r="B11" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="111"/>
-      <c r="D11" s="111"/>
-      <c r="E11" s="112"/>
+      <c r="C11" s="118"/>
+      <c r="D11" s="118"/>
+      <c r="E11" s="119"/>
       <c r="F11" s="50"/>
       <c r="G11" s="51"/>
       <c r="H11" s="51"/>
@@ -2946,47 +3072,47 @@
       <c r="J11" s="53"/>
       <c r="K11" s="14"/>
       <c r="L11" s="14"/>
-      <c r="M11" s="106" t="s">
+      <c r="M11" s="107" t="s">
         <v>8</v>
       </c>
-      <c r="N11" s="107"/>
-      <c r="O11" s="107"/>
-      <c r="P11" s="107"/>
-      <c r="Q11" s="107"/>
-      <c r="R11" s="107"/>
-      <c r="S11" s="108"/>
+      <c r="N11" s="108"/>
+      <c r="O11" s="108"/>
+      <c r="P11" s="108"/>
+      <c r="Q11" s="108"/>
+      <c r="R11" s="108"/>
+      <c r="S11" s="109"/>
     </row>
     <row r="12" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="113"/>
-      <c r="C12" s="114"/>
-      <c r="D12" s="114"/>
-      <c r="E12" s="115"/>
+      <c r="B12" s="120"/>
+      <c r="C12" s="121"/>
+      <c r="D12" s="121"/>
+      <c r="E12" s="129"/>
       <c r="F12" s="60"/>
-      <c r="G12" s="123" t="s">
+      <c r="G12" s="126" t="s">
         <v>71</v>
       </c>
-      <c r="H12" s="124"/>
-      <c r="I12" s="124"/>
-      <c r="J12" s="125"/>
+      <c r="H12" s="127"/>
+      <c r="I12" s="127"/>
+      <c r="J12" s="128"/>
       <c r="K12" s="14"/>
       <c r="L12" s="14"/>
       <c r="M12" s="32">
         <v>15</v>
       </c>
-      <c r="N12" s="85" t="s">
+      <c r="N12" s="86" t="s">
         <v>57</v>
       </c>
-      <c r="O12" s="86"/>
-      <c r="P12" s="86"/>
-      <c r="Q12" s="86"/>
-      <c r="R12" s="86"/>
-      <c r="S12" s="87"/>
+      <c r="O12" s="87"/>
+      <c r="P12" s="87"/>
+      <c r="Q12" s="87"/>
+      <c r="R12" s="87"/>
+      <c r="S12" s="88"/>
     </row>
     <row r="13" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="116"/>
-      <c r="C13" s="117"/>
-      <c r="D13" s="117"/>
-      <c r="E13" s="118"/>
+      <c r="B13" s="123"/>
+      <c r="C13" s="124"/>
+      <c r="D13" s="124"/>
+      <c r="E13" s="125"/>
       <c r="F13" s="50"/>
       <c r="G13" s="51"/>
       <c r="H13" s="51"/>
@@ -2997,22 +3123,22 @@
       <c r="M13" s="29">
         <v>15</v>
       </c>
-      <c r="N13" s="88" t="s">
+      <c r="N13" s="89" t="s">
         <v>58</v>
       </c>
-      <c r="O13" s="89"/>
-      <c r="P13" s="89"/>
-      <c r="Q13" s="89"/>
-      <c r="R13" s="89"/>
-      <c r="S13" s="90"/>
+      <c r="O13" s="90"/>
+      <c r="P13" s="90"/>
+      <c r="Q13" s="90"/>
+      <c r="R13" s="90"/>
+      <c r="S13" s="91"/>
     </row>
     <row r="14" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="110" t="s">
+      <c r="B14" s="117" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="111"/>
-      <c r="D14" s="111"/>
-      <c r="E14" s="112"/>
+      <c r="C14" s="118"/>
+      <c r="D14" s="118"/>
+      <c r="E14" s="119"/>
       <c r="F14" s="50"/>
       <c r="G14" s="51"/>
       <c r="H14" s="51"/>
@@ -3021,44 +3147,44 @@
       <c r="M14" s="30">
         <v>16</v>
       </c>
-      <c r="N14" s="85" t="s">
+      <c r="N14" s="86" t="s">
         <v>59</v>
       </c>
-      <c r="O14" s="86"/>
-      <c r="P14" s="86"/>
-      <c r="Q14" s="86"/>
-      <c r="R14" s="86"/>
-      <c r="S14" s="87"/>
+      <c r="O14" s="87"/>
+      <c r="P14" s="87"/>
+      <c r="Q14" s="87"/>
+      <c r="R14" s="87"/>
+      <c r="S14" s="88"/>
     </row>
     <row r="15" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="113"/>
-      <c r="C15" s="114"/>
-      <c r="D15" s="114"/>
-      <c r="E15" s="115"/>
+      <c r="B15" s="120"/>
+      <c r="C15" s="121"/>
+      <c r="D15" s="121"/>
+      <c r="E15" s="129"/>
       <c r="F15" s="59"/>
-      <c r="G15" s="120" t="s">
+      <c r="G15" s="111" t="s">
         <v>68</v>
       </c>
-      <c r="H15" s="121"/>
-      <c r="I15" s="121"/>
-      <c r="J15" s="122"/>
+      <c r="H15" s="112"/>
+      <c r="I15" s="112"/>
+      <c r="J15" s="113"/>
       <c r="M15" s="31">
         <v>16</v>
       </c>
-      <c r="N15" s="97" t="s">
+      <c r="N15" s="98" t="s">
         <v>60</v>
       </c>
-      <c r="O15" s="98"/>
-      <c r="P15" s="98"/>
-      <c r="Q15" s="98"/>
-      <c r="R15" s="98"/>
-      <c r="S15" s="99"/>
+      <c r="O15" s="99"/>
+      <c r="P15" s="99"/>
+      <c r="Q15" s="99"/>
+      <c r="R15" s="99"/>
+      <c r="S15" s="100"/>
     </row>
     <row r="16" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="116"/>
-      <c r="C16" s="117"/>
-      <c r="D16" s="117"/>
-      <c r="E16" s="118"/>
+      <c r="B16" s="123"/>
+      <c r="C16" s="124"/>
+      <c r="D16" s="124"/>
+      <c r="E16" s="125"/>
       <c r="F16" s="50"/>
       <c r="G16" s="51"/>
       <c r="H16" s="51"/>
@@ -3066,12 +3192,12 @@
       <c r="J16" s="53"/>
     </row>
     <row r="17" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="110" t="s">
+      <c r="B17" s="117" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="111"/>
-      <c r="D17" s="111"/>
-      <c r="E17" s="112"/>
+      <c r="C17" s="118"/>
+      <c r="D17" s="118"/>
+      <c r="E17" s="119"/>
       <c r="F17" s="50"/>
       <c r="G17" s="51"/>
       <c r="H17" s="51"/>
@@ -3079,23 +3205,23 @@
       <c r="J17" s="53"/>
     </row>
     <row r="18" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="113"/>
-      <c r="C18" s="114"/>
-      <c r="D18" s="114"/>
-      <c r="E18" s="115"/>
+      <c r="B18" s="120"/>
+      <c r="C18" s="121"/>
+      <c r="D18" s="121"/>
+      <c r="E18" s="129"/>
       <c r="F18" s="59"/>
-      <c r="G18" s="120" t="s">
+      <c r="G18" s="111" t="s">
         <v>69</v>
       </c>
-      <c r="H18" s="121"/>
-      <c r="I18" s="121"/>
-      <c r="J18" s="122"/>
+      <c r="H18" s="112"/>
+      <c r="I18" s="112"/>
+      <c r="J18" s="113"/>
     </row>
     <row r="19" spans="2:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="116"/>
-      <c r="C19" s="117"/>
-      <c r="D19" s="117"/>
-      <c r="E19" s="118"/>
+      <c r="B19" s="123"/>
+      <c r="C19" s="124"/>
+      <c r="D19" s="124"/>
+      <c r="E19" s="125"/>
       <c r="F19" s="54"/>
       <c r="G19" s="51"/>
       <c r="H19" s="51"/>
@@ -3103,12 +3229,12 @@
       <c r="J19" s="53"/>
     </row>
     <row r="20" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="110" t="s">
+      <c r="B20" s="117" t="s">
         <v>50</v>
       </c>
-      <c r="C20" s="111"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="112"/>
+      <c r="C20" s="118"/>
+      <c r="D20" s="118"/>
+      <c r="E20" s="119"/>
       <c r="F20" s="50"/>
       <c r="G20" s="51"/>
       <c r="H20" s="51"/>
@@ -3116,23 +3242,23 @@
       <c r="J20" s="53"/>
     </row>
     <row r="21" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="113"/>
-      <c r="C21" s="114"/>
-      <c r="D21" s="114"/>
-      <c r="E21" s="119"/>
+      <c r="B21" s="120"/>
+      <c r="C21" s="121"/>
+      <c r="D21" s="121"/>
+      <c r="E21" s="122"/>
       <c r="F21" s="61"/>
-      <c r="G21" s="120" t="s">
+      <c r="G21" s="111" t="s">
         <v>51</v>
       </c>
-      <c r="H21" s="121"/>
-      <c r="I21" s="121"/>
-      <c r="J21" s="122"/>
+      <c r="H21" s="112"/>
+      <c r="I21" s="112"/>
+      <c r="J21" s="113"/>
     </row>
     <row r="22" spans="2:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="116"/>
-      <c r="C22" s="117"/>
-      <c r="D22" s="117"/>
-      <c r="E22" s="118"/>
+      <c r="B22" s="123"/>
+      <c r="C22" s="124"/>
+      <c r="D22" s="124"/>
+      <c r="E22" s="125"/>
       <c r="F22" s="55"/>
       <c r="G22" s="55"/>
       <c r="H22" s="55"/>
@@ -3140,8 +3266,18 @@
       <c r="J22" s="44"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="G0wTdc/taBgYkQTP2MZlQUoGU4QlnqnxY81cckRcFSJdy5DIlgSRw+c+/LebvBC/+Ps3u29LeVzGNoMGR8Q/dQ==" saltValue="uH6vYbHzITQ5SW5Zkx/htQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="NfkF4yj+iEgixxkXgGkXwfbmeur8zEMZzhBeiga1PAe+znO1CUs+dZQfNrUkZLGRoA+B1vX0leFgze0sCGq/qA==" saltValue="MqF1cxQrqY3f4SjF1BynVg==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="20">
+    <mergeCell ref="B8:E10"/>
+    <mergeCell ref="B11:E13"/>
+    <mergeCell ref="B4:E7"/>
+    <mergeCell ref="B14:E16"/>
+    <mergeCell ref="B17:E19"/>
+    <mergeCell ref="B20:E22"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="N15:S15"/>
+    <mergeCell ref="G12:J12"/>
     <mergeCell ref="F4:J6"/>
     <mergeCell ref="G7:J7"/>
     <mergeCell ref="G9:J9"/>
@@ -3152,16 +3288,6 @@
     <mergeCell ref="N13:S13"/>
     <mergeCell ref="N14:S14"/>
     <mergeCell ref="G8:I8"/>
-    <mergeCell ref="B20:E22"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="N15:S15"/>
-    <mergeCell ref="G12:J12"/>
-    <mergeCell ref="B8:E10"/>
-    <mergeCell ref="B11:E13"/>
-    <mergeCell ref="B4:E7"/>
-    <mergeCell ref="B14:E16"/>
-    <mergeCell ref="B17:E19"/>
   </mergeCells>
   <conditionalFormatting sqref="F7 F9 F12 F15 F18 F21">
     <cfRule type="expression" dxfId="1" priority="1">
@@ -3172,6 +3298,7 @@
     <hyperlink ref="G8:I8" r:id="rId1" display="Video for this cell" xr:uid="{3187E52B-8B91-4786-9DBC-20BAAB0B9A08}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -3224,30 +3351,30 @@
       <c r="E2" s="27"/>
     </row>
     <row r="3" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D3" s="83" t="s">
+      <c r="D3" s="84" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="100" t="s">
+      <c r="E3" s="101" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="101"/>
-      <c r="G3" s="101"/>
-      <c r="H3" s="101"/>
-      <c r="I3" s="102"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="103"/>
     </row>
     <row r="4" spans="2:11" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="84"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="104"/>
-      <c r="I4" s="105"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="105"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="105"/>
+      <c r="I4" s="106"/>
     </row>
     <row r="5" spans="2:11" ht="16.149999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="81"/>
+      <c r="C5" s="82"/>
       <c r="D5" s="33"/>
     </row>
     <row r="6" spans="2:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3257,15 +3384,15 @@
       <c r="C6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="106" t="s">
+      <c r="E6" s="107" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="107"/>
-      <c r="G6" s="107"/>
-      <c r="H6" s="107"/>
-      <c r="I6" s="107"/>
-      <c r="J6" s="107"/>
-      <c r="K6" s="108"/>
+      <c r="F6" s="108"/>
+      <c r="G6" s="108"/>
+      <c r="H6" s="108"/>
+      <c r="I6" s="108"/>
+      <c r="J6" s="108"/>
+      <c r="K6" s="109"/>
     </row>
     <row r="7" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
@@ -3277,14 +3404,14 @@
       <c r="E7" s="32">
         <v>15</v>
       </c>
-      <c r="F7" s="85" t="s">
+      <c r="F7" s="86" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="86"/>
-      <c r="H7" s="86"/>
-      <c r="I7" s="86"/>
-      <c r="J7" s="86"/>
-      <c r="K7" s="87"/>
+      <c r="G7" s="87"/>
+      <c r="H7" s="87"/>
+      <c r="I7" s="87"/>
+      <c r="J7" s="87"/>
+      <c r="K7" s="88"/>
     </row>
     <row r="8" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
@@ -3296,14 +3423,14 @@
       <c r="E8" s="29">
         <v>15</v>
       </c>
-      <c r="F8" s="88" t="s">
+      <c r="F8" s="89" t="s">
         <v>58</v>
       </c>
-      <c r="G8" s="89"/>
-      <c r="H8" s="89"/>
-      <c r="I8" s="89"/>
-      <c r="J8" s="89"/>
-      <c r="K8" s="90"/>
+      <c r="G8" s="90"/>
+      <c r="H8" s="90"/>
+      <c r="I8" s="90"/>
+      <c r="J8" s="90"/>
+      <c r="K8" s="91"/>
     </row>
     <row r="9" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B9" s="8" t="s">
@@ -3315,14 +3442,14 @@
       <c r="E9" s="30">
         <v>16</v>
       </c>
-      <c r="F9" s="85" t="s">
+      <c r="F9" s="86" t="s">
         <v>59</v>
       </c>
-      <c r="G9" s="86"/>
-      <c r="H9" s="86"/>
-      <c r="I9" s="86"/>
-      <c r="J9" s="86"/>
-      <c r="K9" s="87"/>
+      <c r="G9" s="87"/>
+      <c r="H9" s="87"/>
+      <c r="I9" s="87"/>
+      <c r="J9" s="87"/>
+      <c r="K9" s="88"/>
     </row>
     <row r="10" spans="2:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="9" t="s">
@@ -3334,41 +3461,41 @@
       <c r="E10" s="31">
         <v>16</v>
       </c>
-      <c r="F10" s="97" t="s">
+      <c r="F10" s="98" t="s">
         <v>60</v>
       </c>
-      <c r="G10" s="98"/>
-      <c r="H10" s="98"/>
-      <c r="I10" s="98"/>
-      <c r="J10" s="98"/>
-      <c r="K10" s="99"/>
+      <c r="G10" s="99"/>
+      <c r="H10" s="99"/>
+      <c r="I10" s="99"/>
+      <c r="J10" s="99"/>
+      <c r="K10" s="100"/>
     </row>
     <row r="11" spans="2:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F12" s="82" t="s">
+      <c r="F12" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="G12" s="63"/>
-      <c r="H12" s="63"/>
-      <c r="I12" s="63"/>
-      <c r="J12" s="63"/>
-      <c r="K12" s="64"/>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="64"/>
+      <c r="K12" s="65"/>
     </row>
     <row r="13" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="91" t="s">
+      <c r="B13" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="93"/>
-      <c r="F13" s="68"/>
-      <c r="G13" s="69"/>
-      <c r="H13" s="69"/>
-      <c r="I13" s="69"/>
-      <c r="J13" s="69"/>
-      <c r="K13" s="70"/>
+      <c r="C13" s="94"/>
+      <c r="F13" s="69"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70"/>
+      <c r="I13" s="70"/>
+      <c r="J13" s="70"/>
+      <c r="K13" s="71"/>
     </row>
     <row r="14" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="94"/>
-      <c r="C14" s="96"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="97"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F15" s="11" t="s">
@@ -3711,10 +3838,10 @@
       </c>
     </row>
     <row r="25" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="82" t="s">
+      <c r="B25" s="83" t="s">
         <v>36</v>
       </c>
-      <c r="C25" s="64"/>
+      <c r="C25" s="65"/>
       <c r="F25" s="19">
         <f>Budget!F25</f>
         <v>0</v>
@@ -3741,8 +3868,8 @@
       </c>
     </row>
     <row r="26" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B26" s="65"/>
-      <c r="C26" s="67"/>
+      <c r="B26" s="66"/>
+      <c r="C26" s="68"/>
       <c r="F26" s="19">
         <f>Budget!F26</f>
         <v>0</v>
@@ -3769,8 +3896,8 @@
       </c>
     </row>
     <row r="27" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B27" s="65"/>
-      <c r="C27" s="67"/>
+      <c r="B27" s="66"/>
+      <c r="C27" s="68"/>
       <c r="F27" s="19">
         <f>Budget!F27</f>
         <v>0</v>
@@ -3797,216 +3924,222 @@
       </c>
     </row>
     <row r="28" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="68"/>
-      <c r="C28" s="70"/>
+      <c r="B28" s="69"/>
+      <c r="C28" s="71"/>
     </row>
     <row r="29" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E29" s="71" t="s">
+      <c r="E29" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="F29" s="72"/>
-      <c r="G29" s="72"/>
-      <c r="H29" s="72"/>
-      <c r="I29" s="72"/>
-      <c r="J29" s="72"/>
-      <c r="K29" s="73"/>
-      <c r="M29" s="71" t="s">
+      <c r="F29" s="73"/>
+      <c r="G29" s="73"/>
+      <c r="H29" s="73"/>
+      <c r="I29" s="73"/>
+      <c r="J29" s="73"/>
+      <c r="K29" s="74"/>
+      <c r="M29" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="N29" s="72"/>
-      <c r="O29" s="72"/>
-      <c r="P29" s="72"/>
-      <c r="Q29" s="72"/>
-      <c r="R29" s="72"/>
-      <c r="S29" s="73"/>
+      <c r="N29" s="73"/>
+      <c r="O29" s="73"/>
+      <c r="P29" s="73"/>
+      <c r="Q29" s="73"/>
+      <c r="R29" s="73"/>
+      <c r="S29" s="74"/>
     </row>
     <row r="30" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B30" s="82" t="s">
+      <c r="B30" s="83" t="s">
         <v>38</v>
       </c>
-      <c r="C30" s="64"/>
-      <c r="E30" s="74"/>
-      <c r="F30" s="75"/>
-      <c r="G30" s="75"/>
-      <c r="H30" s="75"/>
-      <c r="I30" s="75"/>
-      <c r="J30" s="75"/>
-      <c r="K30" s="76"/>
-      <c r="M30" s="74"/>
-      <c r="N30" s="75"/>
-      <c r="O30" s="75"/>
-      <c r="P30" s="75"/>
-      <c r="Q30" s="75"/>
-      <c r="R30" s="75"/>
-      <c r="S30" s="76"/>
+      <c r="C30" s="65"/>
+      <c r="E30" s="75"/>
+      <c r="F30" s="76"/>
+      <c r="G30" s="76"/>
+      <c r="H30" s="76"/>
+      <c r="I30" s="76"/>
+      <c r="J30" s="76"/>
+      <c r="K30" s="77"/>
+      <c r="M30" s="75"/>
+      <c r="N30" s="76"/>
+      <c r="O30" s="76"/>
+      <c r="P30" s="76"/>
+      <c r="Q30" s="76"/>
+      <c r="R30" s="76"/>
+      <c r="S30" s="77"/>
     </row>
     <row r="31" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B31" s="65"/>
-      <c r="C31" s="67"/>
-      <c r="E31" s="74"/>
-      <c r="F31" s="75"/>
-      <c r="G31" s="75"/>
-      <c r="H31" s="75"/>
-      <c r="I31" s="75"/>
-      <c r="J31" s="75"/>
-      <c r="K31" s="76"/>
-      <c r="M31" s="74"/>
-      <c r="N31" s="75"/>
-      <c r="O31" s="75"/>
-      <c r="P31" s="75"/>
-      <c r="Q31" s="75"/>
-      <c r="R31" s="75"/>
-      <c r="S31" s="76"/>
+      <c r="B31" s="66"/>
+      <c r="C31" s="68"/>
+      <c r="E31" s="75"/>
+      <c r="F31" s="76"/>
+      <c r="G31" s="76"/>
+      <c r="H31" s="76"/>
+      <c r="I31" s="76"/>
+      <c r="J31" s="76"/>
+      <c r="K31" s="77"/>
+      <c r="M31" s="75"/>
+      <c r="N31" s="76"/>
+      <c r="O31" s="76"/>
+      <c r="P31" s="76"/>
+      <c r="Q31" s="76"/>
+      <c r="R31" s="76"/>
+      <c r="S31" s="77"/>
     </row>
     <row r="32" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="68"/>
-      <c r="C32" s="70"/>
-      <c r="E32" s="74"/>
-      <c r="F32" s="75"/>
-      <c r="G32" s="75"/>
-      <c r="H32" s="75"/>
-      <c r="I32" s="75"/>
-      <c r="J32" s="75"/>
-      <c r="K32" s="76"/>
-      <c r="M32" s="74"/>
-      <c r="N32" s="75"/>
-      <c r="O32" s="75"/>
-      <c r="P32" s="75"/>
-      <c r="Q32" s="75"/>
-      <c r="R32" s="75"/>
-      <c r="S32" s="76"/>
+      <c r="B32" s="69"/>
+      <c r="C32" s="71"/>
+      <c r="E32" s="75"/>
+      <c r="F32" s="76"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="76"/>
+      <c r="I32" s="76"/>
+      <c r="J32" s="76"/>
+      <c r="K32" s="77"/>
+      <c r="M32" s="75"/>
+      <c r="N32" s="76"/>
+      <c r="O32" s="76"/>
+      <c r="P32" s="76"/>
+      <c r="Q32" s="76"/>
+      <c r="R32" s="76"/>
+      <c r="S32" s="77"/>
     </row>
     <row r="33" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E33" s="74"/>
-      <c r="F33" s="75"/>
-      <c r="G33" s="75"/>
-      <c r="H33" s="75"/>
-      <c r="I33" s="75"/>
-      <c r="J33" s="75"/>
-      <c r="K33" s="76"/>
-      <c r="M33" s="74"/>
-      <c r="N33" s="75"/>
-      <c r="O33" s="75"/>
-      <c r="P33" s="75"/>
-      <c r="Q33" s="75"/>
-      <c r="R33" s="75"/>
-      <c r="S33" s="76"/>
+      <c r="E33" s="75"/>
+      <c r="F33" s="76"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="76"/>
+      <c r="I33" s="76"/>
+      <c r="J33" s="76"/>
+      <c r="K33" s="77"/>
+      <c r="M33" s="75"/>
+      <c r="N33" s="76"/>
+      <c r="O33" s="76"/>
+      <c r="P33" s="76"/>
+      <c r="Q33" s="76"/>
+      <c r="R33" s="76"/>
+      <c r="S33" s="77"/>
     </row>
     <row r="34" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E34" s="74"/>
-      <c r="F34" s="75"/>
-      <c r="G34" s="75"/>
-      <c r="H34" s="75"/>
-      <c r="I34" s="75"/>
-      <c r="J34" s="75"/>
-      <c r="K34" s="76"/>
-      <c r="M34" s="74"/>
-      <c r="N34" s="75"/>
-      <c r="O34" s="75"/>
-      <c r="P34" s="75"/>
-      <c r="Q34" s="75"/>
-      <c r="R34" s="75"/>
-      <c r="S34" s="76"/>
+      <c r="E34" s="75"/>
+      <c r="F34" s="76"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="76"/>
+      <c r="I34" s="76"/>
+      <c r="J34" s="76"/>
+      <c r="K34" s="77"/>
+      <c r="M34" s="75"/>
+      <c r="N34" s="76"/>
+      <c r="O34" s="76"/>
+      <c r="P34" s="76"/>
+      <c r="Q34" s="76"/>
+      <c r="R34" s="76"/>
+      <c r="S34" s="77"/>
     </row>
     <row r="35" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E35" s="74"/>
-      <c r="F35" s="75"/>
-      <c r="G35" s="75"/>
-      <c r="H35" s="75"/>
-      <c r="I35" s="75"/>
-      <c r="J35" s="75"/>
-      <c r="K35" s="76"/>
-      <c r="M35" s="74"/>
-      <c r="N35" s="75"/>
-      <c r="O35" s="75"/>
-      <c r="P35" s="75"/>
-      <c r="Q35" s="75"/>
-      <c r="R35" s="75"/>
-      <c r="S35" s="76"/>
+      <c r="E35" s="75"/>
+      <c r="F35" s="76"/>
+      <c r="G35" s="76"/>
+      <c r="H35" s="76"/>
+      <c r="I35" s="76"/>
+      <c r="J35" s="76"/>
+      <c r="K35" s="77"/>
+      <c r="M35" s="75"/>
+      <c r="N35" s="76"/>
+      <c r="O35" s="76"/>
+      <c r="P35" s="76"/>
+      <c r="Q35" s="76"/>
+      <c r="R35" s="76"/>
+      <c r="S35" s="77"/>
     </row>
     <row r="36" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E36" s="74"/>
-      <c r="F36" s="75"/>
-      <c r="G36" s="75"/>
-      <c r="H36" s="75"/>
-      <c r="I36" s="75"/>
-      <c r="J36" s="75"/>
-      <c r="K36" s="76"/>
-      <c r="M36" s="74"/>
-      <c r="N36" s="75"/>
-      <c r="O36" s="75"/>
-      <c r="P36" s="75"/>
-      <c r="Q36" s="75"/>
-      <c r="R36" s="75"/>
-      <c r="S36" s="76"/>
+      <c r="E36" s="75"/>
+      <c r="F36" s="76"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="76"/>
+      <c r="I36" s="76"/>
+      <c r="J36" s="76"/>
+      <c r="K36" s="77"/>
+      <c r="M36" s="75"/>
+      <c r="N36" s="76"/>
+      <c r="O36" s="76"/>
+      <c r="P36" s="76"/>
+      <c r="Q36" s="76"/>
+      <c r="R36" s="76"/>
+      <c r="S36" s="77"/>
     </row>
     <row r="37" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E37" s="74"/>
-      <c r="F37" s="75"/>
-      <c r="G37" s="75"/>
-      <c r="H37" s="75"/>
-      <c r="I37" s="75"/>
-      <c r="J37" s="75"/>
-      <c r="K37" s="76"/>
-      <c r="M37" s="74"/>
-      <c r="N37" s="75"/>
-      <c r="O37" s="75"/>
-      <c r="P37" s="75"/>
-      <c r="Q37" s="75"/>
-      <c r="R37" s="75"/>
-      <c r="S37" s="76"/>
+      <c r="E37" s="75"/>
+      <c r="F37" s="76"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="76"/>
+      <c r="I37" s="76"/>
+      <c r="J37" s="76"/>
+      <c r="K37" s="77"/>
+      <c r="M37" s="75"/>
+      <c r="N37" s="76"/>
+      <c r="O37" s="76"/>
+      <c r="P37" s="76"/>
+      <c r="Q37" s="76"/>
+      <c r="R37" s="76"/>
+      <c r="S37" s="77"/>
     </row>
     <row r="38" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E38" s="74"/>
-      <c r="F38" s="75"/>
-      <c r="G38" s="75"/>
-      <c r="H38" s="75"/>
-      <c r="I38" s="75"/>
-      <c r="J38" s="75"/>
-      <c r="K38" s="76"/>
-      <c r="M38" s="74"/>
-      <c r="N38" s="75"/>
-      <c r="O38" s="75"/>
-      <c r="P38" s="75"/>
-      <c r="Q38" s="75"/>
-      <c r="R38" s="75"/>
-      <c r="S38" s="76"/>
+      <c r="E38" s="75"/>
+      <c r="F38" s="76"/>
+      <c r="G38" s="76"/>
+      <c r="H38" s="76"/>
+      <c r="I38" s="76"/>
+      <c r="J38" s="76"/>
+      <c r="K38" s="77"/>
+      <c r="M38" s="75"/>
+      <c r="N38" s="76"/>
+      <c r="O38" s="76"/>
+      <c r="P38" s="76"/>
+      <c r="Q38" s="76"/>
+      <c r="R38" s="76"/>
+      <c r="S38" s="77"/>
     </row>
     <row r="39" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E39" s="74"/>
-      <c r="F39" s="75"/>
-      <c r="G39" s="75"/>
-      <c r="H39" s="75"/>
-      <c r="I39" s="75"/>
-      <c r="J39" s="75"/>
-      <c r="K39" s="76"/>
-      <c r="M39" s="74"/>
-      <c r="N39" s="75"/>
-      <c r="O39" s="75"/>
-      <c r="P39" s="75"/>
-      <c r="Q39" s="75"/>
-      <c r="R39" s="75"/>
-      <c r="S39" s="76"/>
+      <c r="E39" s="75"/>
+      <c r="F39" s="76"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="76"/>
+      <c r="I39" s="76"/>
+      <c r="J39" s="76"/>
+      <c r="K39" s="77"/>
+      <c r="M39" s="75"/>
+      <c r="N39" s="76"/>
+      <c r="O39" s="76"/>
+      <c r="P39" s="76"/>
+      <c r="Q39" s="76"/>
+      <c r="R39" s="76"/>
+      <c r="S39" s="77"/>
     </row>
     <row r="40" spans="5:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E40" s="77"/>
-      <c r="F40" s="78"/>
-      <c r="G40" s="78"/>
-      <c r="H40" s="78"/>
-      <c r="I40" s="78"/>
-      <c r="J40" s="78"/>
-      <c r="K40" s="79"/>
-      <c r="M40" s="77"/>
-      <c r="N40" s="78"/>
-      <c r="O40" s="78"/>
-      <c r="P40" s="78"/>
-      <c r="Q40" s="78"/>
-      <c r="R40" s="78"/>
-      <c r="S40" s="79"/>
+      <c r="E40" s="78"/>
+      <c r="F40" s="79"/>
+      <c r="G40" s="79"/>
+      <c r="H40" s="79"/>
+      <c r="I40" s="79"/>
+      <c r="J40" s="79"/>
+      <c r="K40" s="80"/>
+      <c r="M40" s="78"/>
+      <c r="N40" s="79"/>
+      <c r="O40" s="79"/>
+      <c r="P40" s="79"/>
+      <c r="Q40" s="79"/>
+      <c r="R40" s="79"/>
+      <c r="S40" s="80"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="cdv/AvFh6srGwbB7utym/s5Rto4SgYVsrqY0f4ta+9TA3R9+USfKRAEajm2Nsa5BKLVlVu6MEYwkKIOOzax3VA==" saltValue="19VEwvYrnvwxOou5gDKwaQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="14">
+    <mergeCell ref="F8:K8"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:I4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="E6:K6"/>
+    <mergeCell ref="F7:K7"/>
     <mergeCell ref="M29:S40"/>
     <mergeCell ref="B30:C32"/>
     <mergeCell ref="F9:K9"/>
@@ -4015,12 +4148,6 @@
     <mergeCell ref="B13:C14"/>
     <mergeCell ref="B25:C28"/>
     <mergeCell ref="E29:K40"/>
-    <mergeCell ref="F8:K8"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:I4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="E6:K6"/>
-    <mergeCell ref="F7:K7"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D3" r:id="rId1" display="Video" xr:uid="{299DFAA1-25BE-465C-8E9D-C2A88F14D04A}"/>
@@ -4045,34 +4172,34 @@
     <row r="2" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:19" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="82" t="s">
+      <c r="B4" s="83" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="63" t="s">
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="64"/>
-      <c r="M4" s="80" t="s">
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="65"/>
+      <c r="M4" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="81"/>
+      <c r="N4" s="82"/>
     </row>
     <row r="5" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="65"/>
-      <c r="C5" s="109"/>
-      <c r="D5" s="109"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="109"/>
-      <c r="G5" s="109"/>
-      <c r="H5" s="109"/>
-      <c r="I5" s="109"/>
-      <c r="J5" s="67"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="110"/>
+      <c r="G5" s="110"/>
+      <c r="H5" s="110"/>
+      <c r="I5" s="110"/>
+      <c r="J5" s="68"/>
       <c r="M5" s="3" t="s">
         <v>9</v>
       </c>
@@ -4081,15 +4208,15 @@
       </c>
     </row>
     <row r="6" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="65"/>
-      <c r="C6" s="109"/>
-      <c r="D6" s="109"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="69"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="70"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="110"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="71"/>
       <c r="M6" s="5" t="s">
         <v>11</v>
       </c>
@@ -4098,20 +4225,20 @@
       </c>
     </row>
     <row r="7" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="68"/>
-      <c r="C7" s="69"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="70"/>
+      <c r="B7" s="69"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="71"/>
       <c r="F7" s="47">
         <f>Soln!C23</f>
         <v>0</v>
       </c>
-      <c r="G7" s="120" t="s">
+      <c r="G7" s="111" t="s">
         <v>67</v>
       </c>
-      <c r="H7" s="121"/>
-      <c r="I7" s="121"/>
-      <c r="J7" s="122"/>
+      <c r="H7" s="112"/>
+      <c r="I7" s="112"/>
+      <c r="J7" s="113"/>
       <c r="M7" s="7" t="s">
         <v>13</v>
       </c>
@@ -4120,12 +4247,12 @@
       </c>
     </row>
     <row r="8" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="110" t="s">
+      <c r="B8" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="111"/>
-      <c r="D8" s="111"/>
-      <c r="E8" s="112"/>
+      <c r="C8" s="118"/>
+      <c r="D8" s="118"/>
+      <c r="E8" s="119"/>
       <c r="F8" s="50"/>
       <c r="G8" s="51"/>
       <c r="H8" s="51"/>
@@ -4139,20 +4266,20 @@
       </c>
     </row>
     <row r="9" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="113"/>
-      <c r="C9" s="114"/>
-      <c r="D9" s="114"/>
-      <c r="E9" s="115"/>
+      <c r="B9" s="120"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="129"/>
       <c r="F9" s="46">
         <f>1.5*F7</f>
         <v>0</v>
       </c>
-      <c r="G9" s="120" t="s">
+      <c r="G9" s="111" t="s">
         <v>66</v>
       </c>
-      <c r="H9" s="121"/>
-      <c r="I9" s="121"/>
-      <c r="J9" s="122"/>
+      <c r="H9" s="112"/>
+      <c r="I9" s="112"/>
+      <c r="J9" s="113"/>
       <c r="M9" s="9" t="s">
         <v>17</v>
       </c>
@@ -4161,10 +4288,10 @@
       </c>
     </row>
     <row r="10" spans="2:19" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="116"/>
-      <c r="C10" s="117"/>
-      <c r="D10" s="117"/>
-      <c r="E10" s="118"/>
+      <c r="B10" s="123"/>
+      <c r="C10" s="124"/>
+      <c r="D10" s="124"/>
+      <c r="E10" s="125"/>
       <c r="F10" s="50"/>
       <c r="G10" s="51"/>
       <c r="H10" s="51"/>
@@ -4172,12 +4299,12 @@
       <c r="J10" s="53"/>
     </row>
     <row r="11" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="110" t="s">
+      <c r="B11" s="117" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="111"/>
-      <c r="D11" s="111"/>
-      <c r="E11" s="112"/>
+      <c r="C11" s="118"/>
+      <c r="D11" s="118"/>
+      <c r="E11" s="119"/>
       <c r="F11" s="50"/>
       <c r="G11" s="51"/>
       <c r="H11" s="51"/>
@@ -4185,50 +4312,50 @@
       <c r="J11" s="53"/>
       <c r="K11" s="14"/>
       <c r="L11" s="14"/>
-      <c r="M11" s="106" t="s">
+      <c r="M11" s="107" t="s">
         <v>8</v>
       </c>
-      <c r="N11" s="107"/>
-      <c r="O11" s="107"/>
-      <c r="P11" s="107"/>
-      <c r="Q11" s="107"/>
-      <c r="R11" s="107"/>
-      <c r="S11" s="108"/>
+      <c r="N11" s="108"/>
+      <c r="O11" s="108"/>
+      <c r="P11" s="108"/>
+      <c r="Q11" s="108"/>
+      <c r="R11" s="108"/>
+      <c r="S11" s="109"/>
     </row>
     <row r="12" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="113"/>
-      <c r="C12" s="114"/>
-      <c r="D12" s="114"/>
-      <c r="E12" s="115"/>
+      <c r="B12" s="120"/>
+      <c r="C12" s="121"/>
+      <c r="D12" s="121"/>
+      <c r="E12" s="129"/>
       <c r="F12" s="48" t="e">
         <f>F7/F9</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G12" s="123" t="s">
+      <c r="G12" s="126" t="s">
         <v>70</v>
       </c>
-      <c r="H12" s="124"/>
-      <c r="I12" s="124"/>
-      <c r="J12" s="125"/>
+      <c r="H12" s="127"/>
+      <c r="I12" s="127"/>
+      <c r="J12" s="128"/>
       <c r="K12" s="14"/>
       <c r="L12" s="14"/>
       <c r="M12" s="32">
         <v>15</v>
       </c>
-      <c r="N12" s="85" t="s">
+      <c r="N12" s="86" t="s">
         <v>57</v>
       </c>
-      <c r="O12" s="86"/>
-      <c r="P12" s="86"/>
-      <c r="Q12" s="86"/>
-      <c r="R12" s="86"/>
-      <c r="S12" s="87"/>
+      <c r="O12" s="87"/>
+      <c r="P12" s="87"/>
+      <c r="Q12" s="87"/>
+      <c r="R12" s="87"/>
+      <c r="S12" s="88"/>
     </row>
     <row r="13" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="116"/>
-      <c r="C13" s="117"/>
-      <c r="D13" s="117"/>
-      <c r="E13" s="118"/>
+      <c r="B13" s="123"/>
+      <c r="C13" s="124"/>
+      <c r="D13" s="124"/>
+      <c r="E13" s="125"/>
       <c r="F13" s="50"/>
       <c r="G13" s="51"/>
       <c r="H13" s="51"/>
@@ -4239,22 +4366,22 @@
       <c r="M13" s="29">
         <v>15</v>
       </c>
-      <c r="N13" s="88" t="s">
+      <c r="N13" s="89" t="s">
         <v>58</v>
       </c>
-      <c r="O13" s="89"/>
-      <c r="P13" s="89"/>
-      <c r="Q13" s="89"/>
-      <c r="R13" s="89"/>
-      <c r="S13" s="90"/>
+      <c r="O13" s="90"/>
+      <c r="P13" s="90"/>
+      <c r="Q13" s="90"/>
+      <c r="R13" s="90"/>
+      <c r="S13" s="91"/>
     </row>
     <row r="14" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="110" t="s">
+      <c r="B14" s="117" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="111"/>
-      <c r="D14" s="111"/>
-      <c r="E14" s="112"/>
+      <c r="C14" s="118"/>
+      <c r="D14" s="118"/>
+      <c r="E14" s="119"/>
       <c r="F14" s="50"/>
       <c r="G14" s="51"/>
       <c r="H14" s="51"/>
@@ -4263,47 +4390,47 @@
       <c r="M14" s="30">
         <v>16</v>
       </c>
-      <c r="N14" s="85" t="s">
+      <c r="N14" s="86" t="s">
         <v>59</v>
       </c>
-      <c r="O14" s="86"/>
-      <c r="P14" s="86"/>
-      <c r="Q14" s="86"/>
-      <c r="R14" s="86"/>
-      <c r="S14" s="87"/>
+      <c r="O14" s="87"/>
+      <c r="P14" s="87"/>
+      <c r="Q14" s="87"/>
+      <c r="R14" s="87"/>
+      <c r="S14" s="88"/>
     </row>
     <row r="15" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="113"/>
-      <c r="C15" s="114"/>
-      <c r="D15" s="114"/>
-      <c r="E15" s="115"/>
+      <c r="B15" s="120"/>
+      <c r="C15" s="121"/>
+      <c r="D15" s="121"/>
+      <c r="E15" s="129"/>
       <c r="F15" s="46">
         <f>F9*(1+10%)</f>
         <v>0</v>
       </c>
-      <c r="G15" s="120" t="s">
+      <c r="G15" s="111" t="s">
         <v>68</v>
       </c>
-      <c r="H15" s="121"/>
-      <c r="I15" s="121"/>
-      <c r="J15" s="122"/>
+      <c r="H15" s="112"/>
+      <c r="I15" s="112"/>
+      <c r="J15" s="113"/>
       <c r="M15" s="31">
         <v>16</v>
       </c>
-      <c r="N15" s="97" t="s">
+      <c r="N15" s="98" t="s">
         <v>60</v>
       </c>
-      <c r="O15" s="98"/>
-      <c r="P15" s="98"/>
-      <c r="Q15" s="98"/>
-      <c r="R15" s="98"/>
-      <c r="S15" s="99"/>
+      <c r="O15" s="99"/>
+      <c r="P15" s="99"/>
+      <c r="Q15" s="99"/>
+      <c r="R15" s="99"/>
+      <c r="S15" s="100"/>
     </row>
     <row r="16" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="116"/>
-      <c r="C16" s="117"/>
-      <c r="D16" s="117"/>
-      <c r="E16" s="118"/>
+      <c r="B16" s="123"/>
+      <c r="C16" s="124"/>
+      <c r="D16" s="124"/>
+      <c r="E16" s="125"/>
       <c r="F16" s="50"/>
       <c r="G16" s="51"/>
       <c r="H16" s="51"/>
@@ -4311,12 +4438,12 @@
       <c r="J16" s="53"/>
     </row>
     <row r="17" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="110" t="s">
+      <c r="B17" s="117" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="111"/>
-      <c r="D17" s="111"/>
-      <c r="E17" s="112"/>
+      <c r="C17" s="118"/>
+      <c r="D17" s="118"/>
+      <c r="E17" s="119"/>
       <c r="F17" s="50"/>
       <c r="G17" s="51"/>
       <c r="H17" s="51"/>
@@ -4324,26 +4451,26 @@
       <c r="J17" s="53"/>
     </row>
     <row r="18" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="113"/>
-      <c r="C18" s="114"/>
-      <c r="D18" s="114"/>
-      <c r="E18" s="115"/>
+      <c r="B18" s="120"/>
+      <c r="C18" s="121"/>
+      <c r="D18" s="121"/>
+      <c r="E18" s="129"/>
       <c r="F18" s="46" t="e">
         <f>F12*F15</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G18" s="120" t="s">
+      <c r="G18" s="111" t="s">
         <v>69</v>
       </c>
-      <c r="H18" s="121"/>
-      <c r="I18" s="121"/>
-      <c r="J18" s="122"/>
+      <c r="H18" s="112"/>
+      <c r="I18" s="112"/>
+      <c r="J18" s="113"/>
     </row>
     <row r="19" spans="2:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="116"/>
-      <c r="C19" s="117"/>
-      <c r="D19" s="117"/>
-      <c r="E19" s="118"/>
+      <c r="B19" s="123"/>
+      <c r="C19" s="124"/>
+      <c r="D19" s="124"/>
+      <c r="E19" s="125"/>
       <c r="F19" s="54"/>
       <c r="G19" s="51"/>
       <c r="H19" s="51"/>
@@ -4351,12 +4478,12 @@
       <c r="J19" s="53"/>
     </row>
     <row r="20" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="110" t="s">
+      <c r="B20" s="117" t="s">
         <v>50</v>
       </c>
-      <c r="C20" s="111"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="112"/>
+      <c r="C20" s="118"/>
+      <c r="D20" s="118"/>
+      <c r="E20" s="119"/>
       <c r="F20" s="50"/>
       <c r="G20" s="51"/>
       <c r="H20" s="51"/>
@@ -4364,26 +4491,26 @@
       <c r="J20" s="53"/>
     </row>
     <row r="21" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="113"/>
-      <c r="C21" s="114"/>
-      <c r="D21" s="114"/>
-      <c r="E21" s="119"/>
+      <c r="B21" s="120"/>
+      <c r="C21" s="121"/>
+      <c r="D21" s="121"/>
+      <c r="E21" s="122"/>
       <c r="F21" s="45" t="e">
         <f>F18/F7-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G21" s="120" t="s">
+      <c r="G21" s="111" t="s">
         <v>51</v>
       </c>
-      <c r="H21" s="121"/>
-      <c r="I21" s="121"/>
-      <c r="J21" s="122"/>
+      <c r="H21" s="112"/>
+      <c r="I21" s="112"/>
+      <c r="J21" s="113"/>
     </row>
     <row r="22" spans="2:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="116"/>
-      <c r="C22" s="117"/>
-      <c r="D22" s="117"/>
-      <c r="E22" s="118"/>
+      <c r="B22" s="123"/>
+      <c r="C22" s="124"/>
+      <c r="D22" s="124"/>
+      <c r="E22" s="125"/>
       <c r="F22" s="55"/>
       <c r="G22" s="55"/>
       <c r="H22" s="55"/>
@@ -4393,11 +4520,12 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="tmZVzQuchFx4+hmWgpIJ/Xs+dtJHoEIpggrKQwV2riBVXZncjb+E//66rxwrmYGvYjZ14gUZB8TBJFFIqvUKmQ==" saltValue="gVCYbawCFDlVV36UwKuBGA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="19">
-    <mergeCell ref="B17:E19"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="B20:E22"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="B11:E13"/>
+    <mergeCell ref="B4:E7"/>
+    <mergeCell ref="F4:J6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="B8:E10"/>
+    <mergeCell ref="G9:J9"/>
     <mergeCell ref="M11:S11"/>
     <mergeCell ref="G12:J12"/>
     <mergeCell ref="N12:S12"/>
@@ -4406,12 +4534,11 @@
     <mergeCell ref="N14:S14"/>
     <mergeCell ref="G15:J15"/>
     <mergeCell ref="N15:S15"/>
-    <mergeCell ref="B4:E7"/>
-    <mergeCell ref="F4:J6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="B8:E10"/>
-    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="B17:E19"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="B20:E22"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="B11:E13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -4429,178 +4556,178 @@
   <sheetData>
     <row r="2" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B3" s="127" t="s">
+      <c r="B3" s="131" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="127"/>
-      <c r="D3" s="127"/>
-      <c r="E3" s="127"/>
+      <c r="C3" s="131"/>
+      <c r="D3" s="131"/>
+      <c r="E3" s="131"/>
       <c r="F3" s="12"/>
-      <c r="G3" s="126" t="s">
+      <c r="G3" s="130" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="126"/>
-      <c r="J3" s="82" t="s">
+      <c r="H3" s="130"/>
+      <c r="J3" s="83" t="s">
         <v>42</v>
       </c>
-      <c r="K3" s="63"/>
-      <c r="L3" s="63"/>
-      <c r="M3" s="63"/>
-      <c r="N3" s="64"/>
+      <c r="K3" s="64"/>
+      <c r="L3" s="64"/>
+      <c r="M3" s="64"/>
+      <c r="N3" s="65"/>
     </row>
     <row r="4" spans="2:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="114"/>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="66"/>
-      <c r="L4" s="66"/>
-      <c r="M4" s="66"/>
-      <c r="N4" s="67"/>
+      <c r="C4" s="121"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="J4" s="66"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
+      <c r="N4" s="68"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B5" s="114"/>
-      <c r="C5" s="114"/>
-      <c r="D5" s="114"/>
-      <c r="E5" s="114"/>
+      <c r="B5" s="121"/>
+      <c r="C5" s="121"/>
+      <c r="D5" s="121"/>
+      <c r="E5" s="121"/>
       <c r="F5" s="12"/>
-      <c r="G5" s="126" t="s">
+      <c r="G5" s="130" t="s">
         <v>44</v>
       </c>
-      <c r="H5" s="126"/>
-      <c r="J5" s="65"/>
-      <c r="K5" s="66"/>
-      <c r="L5" s="66"/>
-      <c r="M5" s="66"/>
-      <c r="N5" s="67"/>
+      <c r="H5" s="130"/>
+      <c r="J5" s="66"/>
+      <c r="K5" s="67"/>
+      <c r="L5" s="67"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="68"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B6" s="114"/>
-      <c r="C6" s="114"/>
-      <c r="D6" s="114"/>
-      <c r="E6" s="114"/>
-      <c r="J6" s="65"/>
-      <c r="K6" s="66"/>
-      <c r="L6" s="66"/>
-      <c r="M6" s="66"/>
-      <c r="N6" s="67"/>
+      <c r="B6" s="121"/>
+      <c r="C6" s="121"/>
+      <c r="D6" s="121"/>
+      <c r="E6" s="121"/>
+      <c r="J6" s="66"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="67"/>
+      <c r="N6" s="68"/>
     </row>
     <row r="7" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="114" t="s">
+      <c r="B7" s="121" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="114"/>
-      <c r="D7" s="114"/>
-      <c r="E7" s="114"/>
-      <c r="J7" s="68"/>
-      <c r="K7" s="69"/>
-      <c r="L7" s="69"/>
-      <c r="M7" s="69"/>
-      <c r="N7" s="70"/>
+      <c r="C7" s="121"/>
+      <c r="D7" s="121"/>
+      <c r="E7" s="121"/>
+      <c r="J7" s="69"/>
+      <c r="K7" s="70"/>
+      <c r="L7" s="70"/>
+      <c r="M7" s="70"/>
+      <c r="N7" s="71"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B8" s="114"/>
-      <c r="C8" s="114"/>
-      <c r="D8" s="114"/>
-      <c r="E8" s="114"/>
+      <c r="B8" s="121"/>
+      <c r="C8" s="121"/>
+      <c r="D8" s="121"/>
+      <c r="E8" s="121"/>
       <c r="F8" s="12"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B9" s="114"/>
-      <c r="C9" s="114"/>
-      <c r="D9" s="114"/>
-      <c r="E9" s="114"/>
+      <c r="B9" s="121"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="121"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B10" s="114" t="s">
+      <c r="B10" s="121" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="114"/>
-      <c r="D10" s="114"/>
-      <c r="E10" s="114"/>
+      <c r="C10" s="121"/>
+      <c r="D10" s="121"/>
+      <c r="E10" s="121"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B11" s="114"/>
-      <c r="C11" s="114"/>
-      <c r="D11" s="114"/>
-      <c r="E11" s="114"/>
+      <c r="B11" s="121"/>
+      <c r="C11" s="121"/>
+      <c r="D11" s="121"/>
+      <c r="E11" s="121"/>
       <c r="F11" s="12"/>
-      <c r="G11" s="126" t="s">
+      <c r="G11" s="130" t="s">
         <v>47</v>
       </c>
-      <c r="H11" s="126"/>
+      <c r="H11" s="130"/>
       <c r="K11" s="14"/>
       <c r="L11" s="14"/>
       <c r="M11" s="14"/>
       <c r="N11" s="14"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B12" s="114"/>
-      <c r="C12" s="114"/>
-      <c r="D12" s="114"/>
-      <c r="E12" s="114"/>
+      <c r="B12" s="121"/>
+      <c r="C12" s="121"/>
+      <c r="D12" s="121"/>
+      <c r="E12" s="121"/>
       <c r="K12" s="14"/>
       <c r="L12" s="14"/>
       <c r="M12" s="14"/>
       <c r="N12" s="14"/>
     </row>
     <row r="13" spans="2:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="114" t="s">
+      <c r="B13" s="121" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="114"/>
-      <c r="D13" s="114"/>
-      <c r="E13" s="114"/>
+      <c r="C13" s="121"/>
+      <c r="D13" s="121"/>
+      <c r="E13" s="121"/>
       <c r="K13" s="14"/>
       <c r="L13" s="14"/>
       <c r="M13" s="14"/>
       <c r="N13" s="14"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B14" s="114"/>
-      <c r="C14" s="114"/>
-      <c r="D14" s="114"/>
-      <c r="E14" s="114"/>
+      <c r="B14" s="121"/>
+      <c r="C14" s="121"/>
+      <c r="D14" s="121"/>
+      <c r="E14" s="121"/>
       <c r="F14" s="12"/>
-      <c r="G14" s="126" t="s">
+      <c r="G14" s="130" t="s">
         <v>49</v>
       </c>
-      <c r="H14" s="126"/>
+      <c r="H14" s="130"/>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B15" s="114"/>
-      <c r="C15" s="114"/>
-      <c r="D15" s="114"/>
-      <c r="E15" s="114"/>
+      <c r="B15" s="121"/>
+      <c r="C15" s="121"/>
+      <c r="D15" s="121"/>
+      <c r="E15" s="121"/>
     </row>
     <row r="16" spans="2:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="114" t="s">
+      <c r="B16" s="121" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="114"/>
-      <c r="D16" s="114"/>
-      <c r="E16" s="114"/>
+      <c r="C16" s="121"/>
+      <c r="D16" s="121"/>
+      <c r="E16" s="121"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="114"/>
-      <c r="C17" s="114"/>
-      <c r="D17" s="114"/>
-      <c r="E17" s="114"/>
+      <c r="B17" s="121"/>
+      <c r="C17" s="121"/>
+      <c r="D17" s="121"/>
+      <c r="E17" s="121"/>
       <c r="F17" s="12"/>
-      <c r="G17" s="126" t="s">
+      <c r="G17" s="130" t="s">
         <v>51</v>
       </c>
-      <c r="H17" s="126"/>
-      <c r="I17" s="126"/>
+      <c r="H17" s="130"/>
+      <c r="I17" s="130"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B18" s="114"/>
-      <c r="C18" s="114"/>
-      <c r="D18" s="114"/>
-      <c r="E18" s="114"/>
+      <c r="B18" s="121"/>
+      <c r="C18" s="121"/>
+      <c r="D18" s="121"/>
+      <c r="E18" s="121"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -4627,60 +4754,60 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="128" t="s">
+      <c r="A1" s="132" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="128"/>
-      <c r="C1" s="128"/>
-      <c r="D1" s="128"/>
-      <c r="E1" s="128"/>
-      <c r="F1" s="128"/>
-      <c r="G1" s="128"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="128"/>
-      <c r="B2" s="128"/>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="128"/>
-      <c r="G2" s="128"/>
+      <c r="A2" s="132"/>
+      <c r="B2" s="132"/>
+      <c r="C2" s="132"/>
+      <c r="D2" s="132"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="132"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="128"/>
-      <c r="B3" s="128"/>
-      <c r="C3" s="128"/>
-      <c r="D3" s="128"/>
-      <c r="E3" s="128"/>
-      <c r="F3" s="128"/>
-      <c r="G3" s="128"/>
+      <c r="A3" s="132"/>
+      <c r="B3" s="132"/>
+      <c r="C3" s="132"/>
+      <c r="D3" s="132"/>
+      <c r="E3" s="132"/>
+      <c r="F3" s="132"/>
+      <c r="G3" s="132"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="128"/>
-      <c r="B4" s="128"/>
-      <c r="C4" s="128"/>
-      <c r="D4" s="128"/>
-      <c r="E4" s="128"/>
-      <c r="F4" s="128"/>
-      <c r="G4" s="128"/>
+      <c r="A4" s="132"/>
+      <c r="B4" s="132"/>
+      <c r="C4" s="132"/>
+      <c r="D4" s="132"/>
+      <c r="E4" s="132"/>
+      <c r="F4" s="132"/>
+      <c r="G4" s="132"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="128"/>
-      <c r="B5" s="128"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="128"/>
-      <c r="E5" s="128"/>
-      <c r="F5" s="128"/>
-      <c r="G5" s="128"/>
+      <c r="A5" s="132"/>
+      <c r="B5" s="132"/>
+      <c r="C5" s="132"/>
+      <c r="D5" s="132"/>
+      <c r="E5" s="132"/>
+      <c r="F5" s="132"/>
+      <c r="G5" s="132"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="128"/>
-      <c r="B6" s="128"/>
-      <c r="C6" s="128"/>
-      <c r="D6" s="128"/>
-      <c r="E6" s="128"/>
-      <c r="F6" s="128"/>
-      <c r="G6" s="128"/>
+      <c r="A6" s="132"/>
+      <c r="B6" s="132"/>
+      <c r="C6" s="132"/>
+      <c r="D6" s="132"/>
+      <c r="E6" s="132"/>
+      <c r="F6" s="132"/>
+      <c r="G6" s="132"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4692,6 +4819,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cca9fd2d-ef84-45c9-8063-8f4bd4c29606">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C289946819CFF499E91D197BC975371" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="674b7a4e239a9748c7aaa97e309327a4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cca9fd2d-ef84-45c9-8063-8f4bd4c29606" xmlns:ns3="18557d39-01b8-4d71-9479-3fad465290ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="600253478e594d1349e02792803dc53a" ns2:_="" ns3:_="">
     <xsd:import namespace="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
@@ -4908,26 +5054,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9BBA8FE-E6DA-4827-85B8-6FA8D6DB8DFA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cca9fd2d-ef84-45c9-8063-8f4bd4c29606">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{619E3EE9-834C-43AE-8A34-8B87F1488608}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1549A78A-B0D3-45CB-AB15-676AD9DAC4AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4944,22 +5089,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{619E3EE9-834C-43AE-8A34-8B87F1488608}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9BBA8FE-E6DA-4827-85B8-6FA8D6DB8DFA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>